--- a/branches/migration/2026.7.0-template-v0.11.3/ValueSet-mii-qst-pro-eortc-qlq-c30-variant-b_mii-qst-pro-eortc-qlq-c30-variant-b.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/ValueSet-mii-qst-pro-eortc-qlq-c30-variant-b_mii-qst-pro-eortc-qlq-c30-variant-b.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.7.0</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/migration/2026.7.0-template-v0.11.3/ValueSet-mii-qst-pro-eortc-qlq-c30-variant-b_mii-qst-pro-eortc-qlq-c30-variant-b.xlsx
+++ b/branches/migration/2026.7.0-template-v0.11.3/ValueSet-mii-qst-pro-eortc-qlq-c30-variant-b_mii-qst-pro-eortc-qlq-c30-variant-b.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
